--- a/stories/arbres/ATOM-TMP.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Il pleut. Il fait froid. Adam est dans l'entrée avec maman. Maman dit : froid, on prend le manteau. Pluie, on prend les bottes. Adam prend le manteau. Il passe les bras. Il met les bottes. Elles sont jaunes. Ils vont au marché. L'eau fait plic sur les bottes. Adam a chaud dans le manteau. Ils achètent du pain. Ils rentrent. Adam pose le manteau. Il range les bottes près de la porte.</t>
+          <t>Il pleut. Il fait froid. Adam est dans l'entrée avec maman. Froid, on prend le manteau. Pluie, on prend les bottes. Adam prend le manteau. Il passe les bras. Il met les bottes. Elles sont jaunes. Ils vont au marché. L'eau fait plic sur les bottes. Adam a chaud dans le manteau. Ils achètent du pain. Ils rentrent. Adam pose le manteau. Il range les bottes près de la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Il pleut. Il fait froid. Adam est dans l'entrée avec maman.
+maman|Froid, on prend le manteau. Pluie, on prend les bottes.
+narrateur|Adam prend le manteau. Il passe les bras. Il met les bottes. Elles sont jaunes. Ils vont au marché. L'eau fait plic sur les bottes. Adam a chaud dans le manteau. Ils achètent du pain. Ils rentrent. Adam pose le manteau. Il range les bottes près de la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il fait froid et il pleut. Que met Adam ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a mis le manteau. Il a mis les bottes. Froid et pluie.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose le pain. Adam touche ses bottes sèches.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Adam prend le manteau. Il passe les bras. Il met les bottes. Elles sont jaunes. Ils vont au marché. L'eau fait plic sur les bottes. Adam a chaud dans le manteau. Ils achètent du pain. Ils rentrent. Adam pose le manteau. Il range les bottes près de la porte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Il fait froid et il pleut. Que met Adam ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Adam a mis le manteau. Il a mis les bottes. Froid et pluie.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Maman pose le pain. Adam touche ses bottes sèches.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adam met manteau et bottes sous la pluie</t>
+          <t>La cabane sous la gouttière</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut rejoindre la cabane au fond du jardin. La pluie est forte. La gouttière déborde devant la porte. Ils passent sur le côté. Ils écoutent le toit.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Il pleut. Il fait froid. Adam est dans l'entrée avec maman. Froid, on prend le manteau. Pluie, on prend les bottes. Adam prend le manteau. Il passe les bras. Il met les bottes. Elles sont jaunes. Ils vont au marché. L'eau fait plic sur les bottes. Adam a chaud dans le manteau. Ils achètent du pain. Ils rentrent. Adam pose le manteau. Il range les bottes près de la porte.</t>
+          <t>La gouttière déborde dans le bac à fleurs. L'eau tombe en rideau devant les géraniums. Le jardin est un grand bruit. Nino vit ici, avec maman. La cabane de planches attend au fond. Sa porte verte est à peine visible. Tu entends la gouttière ? Oui, maman. Je veux aller dans la cabane. Sous cette pluie-là ? Oui. Pour écouter le toit. En ce moment, Nino prend le manteau épais. Il passe les bras. Le tissu sent encore la pluie d'hier. Maman tend les bottes jaunes. Nino les enfile près du paillasson. Prêt ? Prêt. Ils ouvrent la porte. La pluie leur tape les capuches. Le chemin de dalles a disparu sous l'eau. Ils marchent quand même. Les bottes font ploc, ploc, ploc. Devant la cabane, la gouttière verse un mur d'eau. On ne peut pas entrer. Le rideau est trop fort. On passe sur le côté ? Nino glisse le long du mur. L'herbe est haute et mouillée. Maman suit. Ils rejoignent la petite fenêtre. Nino pousse la porte par l'intérieur du cadre. Elle cède. Ils se faufilent. On est dedans ! Bravo. Tu as trouvé le côté. La cabane sent le bois mouillé. La pluie tambourine le toit. Nino s'assoit sur la caisse. Une goutte entre par une fente. Elle tombe sur sa botte. Toc. Le toit parle. Dehors, la gouttière continue son rideau. Dedans, Nino a chaud dans le manteau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Il pleut. Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Adam est dans l'entrée avec maman. Maman dit : froid, on prend le manteau. Pluie, on prend les bottes. Adam prend le manteau. Il passe les bras. Il met les bottes. Elles sont jaunes. Ils vont au marché. L'eau fait plic sur les bottes. Adam a chaud dans le manteau. Ils achètent du pain. Ils rentrent. Adam pose le manteau. Il range les bottes près de la porte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière déborde dans le bac à fleurs. L'eau tombe en rideau devant les géraniums. Le jardin est un grand bruit. Nino vit ici, avec maman. La cabane de planches attend au fond. Sa porte verte est à peine visible. Tu entends la gouttière ? Oui, maman. Je veux aller dans la cabane. Sous cette pluie-là ? Oui. Pour écouter le toit. En ce moment, Nino prend le manteau épais. Il passe les bras. Le tissu sent encore la pluie d'hier. Maman tend les bottes jaunes. Nino les enfile près du paillasson. Prêt ? Prêt. Ils ouvrent la porte. La pluie leur tape les capuches. Le chemin de dalles a disparu sous l'eau. Ils marchent quand même. Les bottes font ploc, ploc, ploc. Devant la cabane, la gouttière verse un mur d'eau. On ne peut pas entrer. Le rideau est trop fort. On passe sur le côté ? Nino glisse le long du mur. L'herbe est haute et mouillée. Maman suit. Ils rejoignent la petite fenêtre. Nino pousse la porte par l'intérieur du cadre. Elle cède. Ils se faufilent. On est dedans ! Bravo. Tu as trouvé le côté. La cabane sent le bois mouillé. La pluie tambourine le toit. Nino s'assoit sur la caisse. Une goutte entre par une fente. Elle tombe sur sa botte. Toc. Le toit parle. Dehors, la gouttière continue son rideau. Dedans, Nino a chaud dans le manteau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Il pleut. Il fait froid. Adam est dans l'entrée avec maman.
-maman|Froid, on prend le manteau. Pluie, on prend les bottes.
-narrateur|Adam prend le manteau. Il passe les bras. Il met les bottes. Elles sont jaunes. Ils vont au marché. L'eau fait plic sur les bottes. Adam a chaud dans le manteau. Ils achètent du pain. Ils rentrent. Adam pose le manteau. Il range les bottes près de la porte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La gouttière déborde dans le bac à fleurs.
+narrateur|L'eau tombe en rideau devant les géraniums.
+narrateur|Le jardin est un grand bruit.
+narrateur|Nino vit ici, avec maman.
+narrateur|La cabane de planches attend au fond.
+narrateur|Sa porte verte est à peine visible.
+maman|Tu entends la gouttière ?
+enfant-m|Oui, maman.
+enfant-m|Je veux aller dans la cabane.
+maman|Sous cette pluie-là ?
+enfant-m|Oui.
+enfant-m|Pour écouter le toit.
+narrateur|En ce moment, Nino prend le manteau épais.
+narrateur|Il passe les bras.
+narrateur|Le tissu sent encore la pluie d'hier.
+narrateur|Maman tend les bottes jaunes.
+narrateur|Nino les enfile près du paillasson.
+maman|Prêt ?
+enfant-m|Prêt.
+narrateur|Ils ouvrent la porte.
+narrateur|La pluie leur tape les capuches.
+narrateur|Le chemin de dalles a disparu sous l'eau.
+narrateur|Ils marchent quand même.
+narrateur|Les bottes font ploc, ploc, ploc.
+narrateur|Devant la cabane, la gouttière verse un mur d'eau.
+enfant-m|On ne peut pas entrer.
+maman|Le rideau est trop fort.
+maman|On passe sur le côté ?
+narrateur|Nino glisse le long du mur.
+narrateur|L'herbe est haute et mouillée.
+narrateur|Maman suit.
+narrateur|Ils rejoignent la petite fenêtre.
+narrateur|Nino pousse la porte par l'intérieur du cadre.
+narrateur|Elle cède.
+narrateur|Ils se faufilent.
+enfant-m|On est dedans !
+maman|Bravo.
+maman|Tu as trouvé le côté.
+narrateur|La cabane sent le bois mouillé.
+narrateur|La pluie tambourine le toit.
+narrateur|Nino s'assoit sur la caisse.
+narrateur|Une goutte entre par une fente.
+narrateur|Elle tombe sur sa botte.
+enfant-m|Toc.
+maman|Le toit parle.
+narrateur|Dehors, la gouttière continue son rideau.
+narrateur|Dedans, Nino a chaud dans le manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1397,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Il fait froid et il pleut. Que met Adam ?</t>
+          <t>Il fait froid, et il pleut fort. Que met Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt; et il pleut. Que met Adam ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il fait froid, et il pleut fort. Que met Nino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1419,14 +1474,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1557,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il fait froid et il pleut. Que met Adam ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Il fait froid, et il pleut fort.
+narrateur|Que met Nino ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a mis le manteau. Il a mis les bottes. Froid et pluie.</t>
+          <t>Nino pose l'oreille contre une planche. Ça roule, au-dessus. C'est l'eau sur le toit. Un seau de bois attend dans le coin. Nino y pose une pomme de pin. Elle écoute aussi. On reste encore un peu ? Oui. La fente laisse encore une goutte. Toc, sur la botte jaune. Nino rit tout bas. Maman s'assoit sur le seuil intérieur. Le rideau d'eau s'affaiblit un peu. La gouttière se calme. On pourra sortir par devant. Bientôt. Ils attendent. Le bois craque, tout doux. Les géraniums, dehors, sont pliés. Nino les voit par la fenêtre verte. Ils ont trop bu. Comme la gouttière.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam a mis le manteau. Il a mis les bottes. &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt; et pluie.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose l'oreille contre une planche. Ça roule, au-dessus. C'est l'eau sur le toit. Un seau de bois attend dans le coin. Nino y pose une pomme de pin. Elle écoute aussi. On reste encore un peu ? Oui. La fente laisse encore une goutte. Toc, sur la botte jaune. Nino rit tout bas. Maman s'assoit sur le seuil intérieur. Le rideau d'eau s'affaiblit un peu. La gouttière se calme. On pourra sortir par devant. Bientôt. Ils attendent. Le bois craque, tout doux. Les géraniums, dehors, sont pliés. Nino les voit par la fenêtre verte. Ils ont trop bu. Comme la gouttière.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1598,7 +1653,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,10 +1729,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam a mis le manteau. Il a mis les bottes. Froid et pluie.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino pose l'oreille contre une planche.
+enfant-m|Ça roule, au-dessus.
+maman|C'est l'eau sur le toit.
+narrateur|Un seau de bois attend dans le coin.
+narrateur|Nino y pose une pomme de pin.
+enfant-m|Elle écoute aussi.
+maman|On reste encore un peu ?
+enfant-m|Oui.
+narrateur|La fente laisse encore une goutte.
+narrateur|Toc, sur la botte jaune.
+narrateur|Nino rit tout bas.
+narrateur|Maman s'assoit sur le seuil intérieur.
+narrateur|Le rideau d'eau s'affaiblit un peu.
+maman|La gouttière se calme.
+enfant-m|On pourra sortir par devant.
+maman|Bientôt.
+narrateur|Ils attendent.
+narrateur|Le bois craque, tout doux.
+narrateur|Les géraniums, dehors, sont pliés.
+narrateur|Nino les voit par la fenêtre verte.
+enfant-m|Ils ont trop bu.
+maman|Comme la gouttière.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose le pain. Adam touche ses bottes sèches.</t>
+          <t>Le rideau d'eau n'est plus qu'un filet. On rentre se sécher ? Oui. Ils sortent par la porte, cette fois. Les dalles réapparaissent. Nino pose la pomme de pin sur la caisse. La cabane garde le bruit du toit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman pose le pain. Adam touche ses bottes sèches.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau d'eau n'est plus qu'un filet. On rentre se sécher ? Oui. Ils sortent par la porte, cette fois. Les dalles réapparaissent. Nino pose la pomme de pin sur la caisse. La cabane garde le bruit du toit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,7 +1845,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1838,10 +1913,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose le pain. Adam touche ses bottes sèches.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le rideau d'eau n'est plus qu'un filet.
+maman|On rentre se sécher ?
+enfant-m|Oui.
+narrateur|Ils sortent par la porte, cette fois.
+narrateur|Les dalles réapparaissent.
+narrateur|Nino pose la pomme de pin sur la caisse.
+narrateur|La cabane garde le bruit du toit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Au fond du jardin, la porte verte se ferme. La gouttière chante plus bas. Le toit a parlé. Oui. Les bottes jaunes sèchent près du paillasson.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Au fond du jardin, la porte verte se ferme. La gouttière chante plus bas. Le toit a parlé. Oui. Les bottes jaunes sèchent près du paillasson.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1934,7 +2014,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2006,10 +2086,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Au fond du jardin, la porte verte se ferme.
+narrateur|La gouttière chante plus bas.
+enfant-m|Le toit a parlé.
+maman|Oui.
+narrateur|Les bottes jaunes sèchent près du paillasson.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée et marché</t>
+          <t>jardin sous l'orage, cabane au fond</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
